--- a/data/b2_centro/B2 Centro 01-2026.xlsx
+++ b/data/b2_centro/B2 Centro 01-2026.xlsx
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>3327.71</v>
+        <v>3242.61</v>
       </c>
     </row>
     <row r="3">
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>78206</v>
+        <v>79825.06</v>
       </c>
     </row>
     <row r="4">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>5758.18</v>
+        <v>5556.22</v>
       </c>
     </row>
     <row r="7">
@@ -5116,12 +5116,12 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1802.63</v>
+        <v>1763.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
@@ -5130,29 +5130,29 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1616.92</v>
+        <v>1826.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1654.57</v>
+        <v>12982.26</v>
       </c>
     </row>
     <row r="10">
@@ -5161,34 +5161,34 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>13610.32</v>
+        <v>4575.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46037</v>
+        <v>46039</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4196.24</v>
+        <v>2853.46</v>
       </c>
     </row>
     <row r="12">
@@ -5197,75 +5197,75 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3168.57</v>
+        <v>5632.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>6198.84</v>
+        <v>2006.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4296.68</v>
+        <v>27634.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>27840.59</v>
+        <v>4126.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46043</v>
+        <v>46047</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5274,11 +5274,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1212.63</v>
+        <v>1957.63</v>
       </c>
     </row>
     <row r="17">
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5714.34</v>
+        <v>6120.71</v>
       </c>
     </row>
     <row r="18">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5722.72</v>
+        <v>5703.28</v>
       </c>
     </row>
   </sheetData>
